--- a/docs/StructureDefinition-BRMedidaObservada.xlsx
+++ b/docs/StructureDefinition-BRMedidaObservada.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-05T10:09:20-03:00</t>
+    <t>2026-06-16T17:47:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -383,7 +383,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -562,7 +562,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -591,7 +591,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -674,7 +674,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -1028,7 +1028,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1106,7 +1106,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1191,7 +1191,7 @@
     <t>Observation.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1231,7 +1231,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1254,7 +1254,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1700,7 +1700,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1779,7 +1779,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1811,7 +1811,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1924,7 +1924,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1952,7 +1952,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -2018,7 +2018,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2068,7 +2068,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -2104,7 +2104,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2141,7 +2141,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2163,7 +2163,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2224,7 +2224,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -5642,7 +5642,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>267</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>277</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>294</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>301</v>
       </c>
@@ -16804,12 +16804,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP118">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/docs/StructureDefinition-BRMedidaObservada.xlsx
+++ b/docs/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRMedidaObservada.xlsx
+++ b/docs/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRMedidaObservada.xlsx
+++ b/docs/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRMedidaObservada.xlsx
+++ b/docs/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
